--- a/Extra/TIẾN ĐỘ HÀNG TUẦN.xlsx
+++ b/Extra/TIẾN ĐỘ HÀNG TUẦN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAEA45CB-5311-4AF9-8254-BA58CB472E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637BC005-02E9-4A34-BE25-BB76990688BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{1470B35E-AD2C-4378-88ED-79DCCDFB3507}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1470B35E-AD2C-4378-88ED-79DCCDFB3507}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="30">
   <si>
     <t>THÀNH VIÊN</t>
   </si>
@@ -106,13 +106,31 @@
   </si>
   <si>
     <t>BẢNG TIẾN ĐỘ NHÓM (TUẦN 6)</t>
+  </si>
+  <si>
+    <t>BẢNG TIẾN ĐỘ NHÓM ( TUẦN 7)</t>
+  </si>
+  <si>
+    <t>Thiết kế lại giao diện Client và tích hợp TcpClientService, DownloadService</t>
+  </si>
+  <si>
+    <t>Sửa lỗi và hoàn thiện giao diện WinForms, cập nhật Program.cs</t>
+  </si>
+  <si>
+    <t>Cải thiện TCP Client Service và cập nhật chức năng download progress</t>
+  </si>
+  <si>
+    <t>Hoàn thiện DownloadService.cs</t>
+  </si>
+  <si>
+    <t>Cải thiện ServerMainForm và bổ sung xử lý lỗi kết nối Client</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +143,15 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
@@ -231,20 +258,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{007145BA-6A51-4F24-9717-9855FAD7FA36}">
-  <dimension ref="A3:D11"/>
+  <dimension ref="A3:D22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.88671875" customWidth="1"/>
@@ -671,6 +704,105 @@
         <v>22</v>
       </c>
     </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+    </row>
+    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Extra/TIẾN ĐỘ HÀNG TUẦN.xlsx
+++ b/Extra/TIẾN ĐỘ HÀNG TUẦN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637BC005-02E9-4A34-BE25-BB76990688BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096B1A55-8887-482E-9F3D-E380E9E51D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1470B35E-AD2C-4378-88ED-79DCCDFB3507}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="38">
   <si>
     <t>THÀNH VIÊN</t>
   </si>
@@ -124,6 +124,30 @@
   </si>
   <si>
     <t>Cải thiện ServerMainForm và bổ sung xử lý lỗi kết nối Client</t>
+  </si>
+  <si>
+    <t>BẢNG TIẾN ĐỘ NHÓM ( TUẦN 8)</t>
+  </si>
+  <si>
+    <t>Cải thiện Server Core</t>
+  </si>
+  <si>
+    <t>Hoàn thiện TCP CLIENT COMMUNICATION</t>
+  </si>
+  <si>
+    <t>Hoàn thiện DOWNLOAD QUEUE &amp; PROGRESS</t>
+  </si>
+  <si>
+    <t>Hoàn thiện SERVER CORE &amp; FILE SYSTEM</t>
+  </si>
+  <si>
+    <t>Hoàn thiện CLIENT HANDLER &amp; GIAO DIỆN SERVER</t>
+  </si>
+  <si>
+    <t>Hoàn thiện  MODEL &amp; CẤU HÌNH CLIENT</t>
+  </si>
+  <si>
+    <t>Hoàn thiện giao diện CLIENT</t>
   </si>
 </sst>
 </file>
@@ -592,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{007145BA-6A51-4F24-9717-9855FAD7FA36}">
-  <dimension ref="A3:D22"/>
+  <dimension ref="A3:D34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.88671875" customWidth="1"/>
@@ -786,8 +810,12 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
+      <c r="C21" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
@@ -800,6 +828,109 @@
         <v>29</v>
       </c>
       <c r="D22" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="13" t="s">
         <v>22</v>
       </c>
     </row>
